--- a/EPD materiali.xlsx
+++ b/EPD materiali.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Tesi_Magistrale\Progetto\Codice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74B8109-7E23-4D7B-BE1B-FC1F95BF3BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EA4096-0BB8-4BDA-9708-2896AC424D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{670B7FBB-75A7-404D-BFF6-8FE2820B436C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>Materiale</t>
   </si>
@@ -117,6 +117,24 @@
   </si>
   <si>
     <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQB11YOuUYgmTovjNcAG9hCYASyuGAAy3tTUz52KTu27P_A?e=E31bvw</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQBRWYwdljN3TLmOJrcNYb7KAZBT-3VBniwkCT6463PuoxM?e=L6Caeg</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQB9m07uy9luRpXc2vw4KkFJAV6PMylaOH3-Tssuf4c0LOQ?e=Sy0EOh</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQAQyYuKv4xYQpEjlH4YktKlAapDT8bJh4ee1pJ30c2DqcY?e=M3SCpW</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQCxtdF31qcPS4z5lTVt83R-AQRj6u4lJPW6zAHVUsnZmD0?e=R2lLda</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQDbmkNkzU9uRLTf4ndkhxbLAUJWd6Cjm7q-LTLGnV5Tc5c?e=MXAOYb</t>
+  </si>
+  <si>
+    <t>https://politoit-my.sharepoint.com/:b:/g/personal/s349000_studenti_polito_it/IQBIKYlQ3trhR5JJvVH8LQpyAQ2jiaNvAjWHNiA2jB4OwQE?e=UMBHIG</t>
   </si>
 </sst>
 </file>
@@ -596,6 +614,9 @@
       <c r="E4" s="2">
         <v>0</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -614,6 +635,9 @@
       <c r="E5" s="2">
         <v>0</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -721,6 +745,9 @@
         <f>(6.78+0.237+4.03)/1000</f>
         <v>1.1047000000000001E-2</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -740,6 +767,9 @@
         <f>(6.84 + 0 + 1.68 )/1000</f>
         <v>8.5199999999999998E-3</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -759,6 +789,9 @@
         <f>(1.56 + 0+ 0.992)/1000</f>
         <v>2.552E-3</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -777,6 +810,9 @@
       <c r="E13" s="2">
         <f>(9.62 + 0.198+2.03)/1000</f>
         <v>1.1847999999999999E-2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -787,6 +823,12 @@
     <hyperlink ref="F9" r:id="rId4" xr:uid="{CEFCD98D-38FB-4906-A268-C5CD0B82924D}"/>
     <hyperlink ref="F7" r:id="rId5" xr:uid="{A6AC7154-19CA-4721-A9C3-C9BB92C24BD6}"/>
     <hyperlink ref="F8" r:id="rId6" xr:uid="{86707B21-18DF-4544-B1AA-9DD03705483F}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{C8020416-2459-4007-9A46-26ABC50F241E}"/>
+    <hyperlink ref="F12" r:id="rId8" xr:uid="{77EB6187-1BE7-4AD8-ADC0-593E541606B0}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{7A3B82DE-6727-4A19-BF7D-72D6CD922F93}"/>
+    <hyperlink ref="F10" r:id="rId10" xr:uid="{0C55A6D9-941B-43D8-83C9-3B1596340811}"/>
+    <hyperlink ref="F5" r:id="rId11" xr:uid="{7AFB0966-598A-49BF-8AE5-8D4B7BB9EFE7}"/>
+    <hyperlink ref="F4" r:id="rId12" xr:uid="{2D91F95F-534B-4778-BEB7-87E71FA40368}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
